--- a/business_forms/035_corporate_innovation_leadership_program_application--business_forms.xlsx
+++ b/business_forms/035_corporate_innovation_leadership_program_application--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'innovation_consultant',_'label':_'innovation_consultant'}</t>
+          <t>innovation_consultant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Innovation Consultant', 'label': 'Innovation Consultant'}</t>
+          <t>Innovation Consultant</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'project_manager',_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Project Manager', 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'operations_manager',_'label':_'operations_manager'}</t>
+          <t>operations_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Operations Manager', 'label': 'Operations Manager'}</t>
+          <t>Operations Manager</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'leadership',_'label':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Leadership', 'label': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'communication',_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Communication', 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'problem_solving',_'label':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Problem Solving', 'label': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
